--- a/web_design_forms/009_website_planning_form--web_design_forms.xlsx
+++ b/web_design_forms/009_website_planning_form--web_design_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -520,15 +520,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>page_1</t>
+          <t>website_details</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>page_1</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Website details</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Describe your website</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>no</t>
@@ -538,20 +542,24 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>page_2</t>
+          <t>company_details</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>company_details</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Company information</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Please provide company details</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>no</t>
@@ -566,15 +574,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>page_3</t>
+          <t>contact_details</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>contact_details</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Contact information</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Enter contact information</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>no</t>
@@ -584,20 +596,24 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>page_4</t>
+          <t>phone_number</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>company_details</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>Phone number</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Enter a valid phone number</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>no</t>
@@ -612,17 +628,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>page_5</t>
+          <t>project_details</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>contact_details</t>
+          <t>Project details</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Provide a valid email address.</t>
+          <t>Describe your project details</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -634,20 +650,24 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>page_6</t>
+          <t>project_deadline</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>phone_number</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Project deadline</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Enter a date for the project deadline</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>no</t>
@@ -662,15 +682,19 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>page_7</t>
+          <t>additional_info</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>project_details</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Additional information</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Add any additional information</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>no</t>
@@ -680,22 +704,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>page_8</t>
+          <t>website_features</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>project_details</t>
+          <t>Website features</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Project details should be as specific as possible.</t>
+          <t>Select the website features</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -707,20 +731,24 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>page_9</t>
+          <t>website_platform</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>website_details</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Website platform</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Select your preferred website platform</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>no</t>
@@ -730,20 +758,24 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>page_10</t>
+          <t>website_content</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>website_details</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>Website content</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Describe your website content</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>no</t>
@@ -753,20 +785,24 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>page_11</t>
+          <t>target_audience</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>website_details</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>Target audience</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Who is your target audience?</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>no</t>
@@ -781,17 +817,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>page_12</t>
+          <t>website_goals</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>website_details</t>
+          <t>Website goals</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Select all that apply</t>
+          <t>What are your website goals?</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -808,15 +844,19 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>page_13</t>
+          <t>website_launch_date</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>page_13</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>Website launch date</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Enter a date for the website launch</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>no</t>
@@ -831,15 +871,19 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>page_14</t>
+          <t>website_launch_time</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>Website launch time</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Enter a time for the website launch</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>no</t>
@@ -849,20 +893,24 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>page_15</t>
+          <t>website_url</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>project_deadline</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>Website URL</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Enter a valid website URL</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>no</t>
@@ -872,20 +920,24 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>page_16</t>
+          <t>website_status</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>page_16</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>Website status</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Select the website status</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>no</t>
@@ -895,20 +947,24 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>page_17</t>
+          <t>website_analytics</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>page_17</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
+          <t>Website analytics</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Select the website analytics</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>no</t>
@@ -918,182 +974,25 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>page_18</t>
+          <t>website_security</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>page_18</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
+          <t>Website security</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Select the website security</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>page_19</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>page_19</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>page_20</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>page_20</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>page_21</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>page_21</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>page_22</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>page_22</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>page_23</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>page_23</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>page_24</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>page_24</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>page_25</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>page_25</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1110,12 +1009,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1138,170 +1037,374 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>page_2_choices</t>
+          <t>company_details_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>page_2_choices</t>
+          <t>company_details_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>page_4_choices</t>
+          <t>website_features_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>page_4_choices</t>
+          <t>website_features_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>page_8_choices</t>
+          <t>website_platform_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>wordpress</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>WordPress</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>page_8_choices</t>
+          <t>website_platform_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>wix</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Wix</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>page_10_choices</t>
+          <t>website_platform_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>squarespace</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Squarespace</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>page_10_choices</t>
+          <t>website_platform_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>webflow</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Webflow</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>page_12_choices</t>
+          <t>target_audience_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>men</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Men</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>page_12_choices</t>
+          <t>target_audience_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>women</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Women</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>target_audience_choices</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>children</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Children</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>website_goals_choices</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>website_goals_choices</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>marketing</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>website_goals_choices</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>informational</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>website_status_choices</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>under_construction</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Under Construction</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>website_status_choices</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>website_status_choices</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>down</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Down</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>website_analytics_choices</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>google_analytics</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Google Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>website_analytics_choices</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>google_ads</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Google Ads</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>website_analytics_choices</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>website_security_choices</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>ssl</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>SSL</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>website_security_choices</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>no_security</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>No security</t>
         </is>
       </c>
     </row>
